--- a/education_forms/003_access_program_proposal_form--education_forms.xlsx
+++ b/education_forms/003_access_program_proposal_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -981,8 +981,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'academic_support',_'value':_'academic_support'}</t>
+          <t>academic_support</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Academic Support', 'value': 'academic_support'}</t>
+          <t>Academic Support</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'financial_assistance',_'value':_'financial_assistance'}</t>
+          <t>financial_assistance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Financial Assistance', 'value': 'financial_assistance'}</t>
+          <t>Financial Assistance</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'extracurricular/club',_'value':_'extracurricular'}</t>
+          <t>extracurricular/club</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Extracurricular/Club', 'value': 'extracurricular'}</t>
+          <t>Extracurricular/Club</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'technology/infrastructure',_'value':_'technology'}</t>
+          <t>technology/infrastructure</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Technology/Infrastructure', 'value': 'technology'}</t>
+          <t>Technology/Infrastructure</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'community_outreach',_'value':_'outreach'}</t>
+          <t>community_outreach</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Community Outreach', 'value': 'outreach'}</t>
+          <t>Community Outreach</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'k-5_students',_'value':_'k5'}</t>
+          <t>k-5_students</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'K-5 Students', 'value': 'k5'}</t>
+          <t>K-5 Students</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'middle_school_students',_'value':_'middle_school'}</t>
+          <t>middle_school_students</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Middle School Students', 'value': 'middle_school'}</t>
+          <t>Middle School Students</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'high_school_students',_'value':_'high_school'}</t>
+          <t>high_school_students</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'High School Students', 'value': 'high_school'}</t>
+          <t>High School Students</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'undergraduate_students',_'value':_'undergraduate'}</t>
+          <t>undergraduate_students</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Undergraduate Students', 'value': 'undergraduate'}</t>
+          <t>Undergraduate Students</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'graduate_students',_'value':_'graduate'}</t>
+          <t>graduate_students</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Graduate Students', 'value': 'graduate'}</t>
+          <t>Graduate Students</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'faculty/staff',_'value':_'faculty_staff'}</t>
+          <t>faculty/staff</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Faculty/Staff', 'value': 'faculty_staff'}</t>
+          <t>Faculty/Staff</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
